--- a/backend/data/financials_by_company/1732.HK.xlsx
+++ b/backend/data/financials_by_company/1732.HK.xlsx
@@ -4000,7 +4000,7 @@
         <v>-5122000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
         <v>0.998</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
         <v>-0.028599992</v>
